--- a/forecasting/MohenTel8800.xlsx
+++ b/forecasting/MohenTel8800.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\OneDrive\Рабочий стол\НИР\Итог\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleks\PycharmProjects\NIR2\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBD6BD4-544C-4BA6-9387-1B1146C9AB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5848BA79-0CDF-46C1-ACDA-A0C2B5925088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16680" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10572" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>I квартал 2021</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>III квартал  2025</t>
+  </si>
+  <si>
+    <t>IV квартал 2025</t>
+  </si>
+  <si>
+    <t>I квартал  2026</t>
   </si>
 </sst>
 </file>
@@ -157,7 +163,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -180,12 +186,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -197,6 +214,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -480,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
@@ -639,6 +659,22 @@
         <v>133</v>
       </c>
     </row>
+    <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
